--- a/tool/kintone-resourse-generator/template/template.xlsx
+++ b/tool/kintone-resourse-generator/template/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248C4C22-434B-40D0-BB17-AC61692E36A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6766EA5A-317F-481F-8BDF-34E00FE62F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>管理者</t>
   </si>
@@ -92,6 +92,13 @@
     <t>スペース名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本文</t>
+    <rPh sb="0" eb="2">
+      <t>ホンブン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -461,30 +468,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.88671875" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/tool/kintone-resourse-generator/template/template.xlsx
+++ b/tool/kintone-resourse-generator/template/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6766EA5A-317F-481F-8BDF-34E00FE62F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FB5A2E-106F-4270-BD4B-BDACFC9B05C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,9 +120,10 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -150,10 +151,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -469,21 +475,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.88671875" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -508,15 +515,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -539,12 +547,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -558,17 +567,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="17.77734375" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -609,16 +617,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="4" max="4" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.77734375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
